--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Downloads 20260424075830.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Downloads 20260424075830.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BC95810-7284-4406-9890-68AE07C13445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DDF99F-68B3-1548-90C9-FDBBADAFDBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8508" yWindow="0" windowWidth="14628" windowHeight="12336" xr2:uid="{D4B10D4A-80E5-4849-BBD6-77A96CE866DF}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23120" windowHeight="15740" xr2:uid="{D4B10D4A-80E5-4849-BBD6-77A96CE866DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Downloads 20260424075830" sheetId="1" r:id="rId1"/>
@@ -639,6 +639,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{564E4D68-0095-974E-A431-DCC62784E5E9}" name="Table1" displayName="Table1" ref="A1:H7" totalsRowShown="0">
+  <autoFilter ref="A1:H7" xr:uid="{564E4D68-0095-974E-A431-DCC62784E5E9}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{9D8536FF-B07B-4B40-B376-1BBBBD7EDBCD}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{BCF09299-32DF-2846-B9B3-06FEC4C6305D}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{F821B252-4F6A-FB4D-BD0E-B3D4424A6CC4}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{A3596EFF-2B17-D04B-9803-462690651B30}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{DE8FBFC6-44DC-814E-9393-B3F8616F4235}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{D8FE773B-054B-1441-8B90-FCADBC2D0BB3}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{5599468F-7336-574F-986C-AFCB67829845}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{502C4B64-413F-E547-9772-3A80C6B14C51}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -959,16 +976,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C837E0B0-DFD9-47E5-BD76-3987BE13F75A}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="58.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="81.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -994,7 +1011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1020,7 +1037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1046,7 +1063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1072,7 +1089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1098,7 +1115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1124,7 +1141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1152,5 +1169,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>